--- a/docs/oc-regiones/gas-licuado-de-petroleo/magallanes.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M724"/>
+  <dimension ref="A1:M725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22471,7 +22471,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1079445-26-CM26</t>
+          <t>855-21-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22496,12 +22496,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22530,13 +22530,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1299.25</v>
+        <v>102.55</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1079445-42-CM26</t>
+          <t>1079445-26-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22595,7 +22595,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>7178.52</v>
+        <v>1299.25</v>
       </c>
     </row>
     <row r="357">
@@ -22731,7 +22731,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>855-21-CM26</t>
+          <t>1079445-42-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22756,12 +22756,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22790,7 +22790,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>102.55</v>
+        <v>7178.52</v>
       </c>
     </row>
     <row r="360">
@@ -22991,7 +22991,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3409-24-CM26</t>
+          <t>1079445-46-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23016,12 +23016,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.101.455-4</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23050,13 +23050,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1282.87</v>
+        <v>1057.47</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1079445-46-CM26</t>
+          <t>3409-24-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23081,12 +23081,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.101.455-4</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1057.47</v>
+        <v>1282.87</v>
       </c>
     </row>
     <row r="365">
@@ -23186,7 +23186,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1470-4-CM26</t>
+          <t>1233613-239-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23206,17 +23206,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>420.39</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="367">
@@ -23381,7 +23381,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>3617-37-CM26</t>
+          <t>1470-4-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -23401,17 +23401,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23440,13 +23440,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>5335.33</v>
+        <v>420.39</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1233613-240-CM26</t>
+          <t>3617-37-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -23471,12 +23471,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1261.17</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="371">
@@ -23576,7 +23576,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1233613-239-CM26</t>
+          <t>1233613-240-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24291,7 +24291,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1536-57-CM26</t>
+          <t>4589-100-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -24311,17 +24311,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -24350,13 +24350,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>4603.65</v>
+        <v>1616.17</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4589-100-CM26</t>
+          <t>4589-101-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -24396,17 +24396,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1616.17</v>
+        <v>2415.92</v>
       </c>
     </row>
     <row r="385">
@@ -24486,7 +24486,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4589-101-CM26</t>
+          <t>1536-57-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24506,17 +24506,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24526,17 +24526,17 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -24545,7 +24545,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2415.92</v>
+        <v>4603.65</v>
       </c>
     </row>
     <row r="387">
@@ -24681,7 +24681,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>958479-60-CM26</t>
+          <t>1470-9-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24706,12 +24706,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.980.720-0</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24740,13 +24740,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2557.93</v>
+        <v>426.32</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3187-72-CM26</t>
+          <t>1470-8-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24766,17 +24766,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.102.041-4</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24805,13 +24805,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1023.17</v>
+        <v>213.16</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1470-8-CM26</t>
+          <t>3187-72-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -24831,17 +24831,17 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>61.102.041-4</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24870,13 +24870,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>213.16</v>
+        <v>1023.17</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1470-9-CM26</t>
+          <t>958479-60-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24901,12 +24901,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>61.980.720-0</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24935,7 +24935,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>426.32</v>
+        <v>2557.93</v>
       </c>
     </row>
     <row r="393">
@@ -25071,7 +25071,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>3412-28-CM26</t>
+          <t>855-37-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25096,12 +25096,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25130,13 +25130,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>892.91</v>
+        <v>151.94</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>855-37-CM26</t>
+          <t>3412-28-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25161,12 +25161,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25195,13 +25195,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>151.94</v>
+        <v>892.91</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4589-119-CM26</t>
+          <t>1079445-113-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25221,17 +25221,17 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -25260,13 +25260,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>817.37</v>
+        <v>1277.13</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1079445-113-CM26</t>
+          <t>4589-119-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25286,17 +25286,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25325,7 +25325,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1277.13</v>
+        <v>817.37</v>
       </c>
     </row>
     <row r="399">
@@ -25396,7 +25396,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>855-39-CM26</t>
+          <t>3595-117-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25421,12 +25421,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -25436,12 +25436,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -25455,13 +25455,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>462.46</v>
+        <v>2318.03</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>3595-116-CM26</t>
+          <t>855-39-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -25486,12 +25486,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -25501,17 +25501,17 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -25520,13 +25520,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1773.65</v>
+        <v>462.46</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>3595-117-CM26</t>
+          <t>3595-116-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -25566,17 +25566,17 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2318.03</v>
+        <v>1773.65</v>
       </c>
     </row>
     <row r="403">
@@ -25721,7 +25721,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1233613-677-CM26</t>
+          <t>3704-65-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -25746,12 +25746,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25780,13 +25780,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>1511.87</v>
+        <v>762.29</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>3704-65-CM26</t>
+          <t>1233613-677-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -25811,12 +25811,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25845,13 +25845,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>762.29</v>
+        <v>1511.87</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1116007-33-CM26</t>
+          <t>1233613-676-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -25871,17 +25871,17 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25910,13 +25910,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2267.8</v>
+        <v>1270.48</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1233613-676-CM26</t>
+          <t>1116007-33-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25936,17 +25936,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25975,13 +25975,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1270.48</v>
+        <v>2267.8</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1079445-132-CM26</t>
+          <t>4589-144-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26001,17 +26001,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26021,17 +26021,17 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -26040,7 +26040,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1047.93</v>
+        <v>1722.26</v>
       </c>
     </row>
     <row r="410">
@@ -26111,7 +26111,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1079445-140-CM26</t>
+          <t>1079445-132-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26170,13 +26170,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>498.81</v>
+        <v>1047.93</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>4589-144-CM26</t>
+          <t>1079445-140-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26196,17 +26196,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -26216,17 +26216,17 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -26235,7 +26235,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1722.26</v>
+        <v>498.81</v>
       </c>
     </row>
     <row r="413">
@@ -26436,7 +26436,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>796297-26-CM26</t>
+          <t>3704-76-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -26461,12 +26461,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -26495,13 +26495,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1433.64</v>
+        <v>666.4</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>3704-76-CM26</t>
+          <t>796297-26-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -26526,12 +26526,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -26560,7 +26560,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>666.4</v>
+        <v>1433.64</v>
       </c>
     </row>
     <row r="418">
@@ -26761,7 +26761,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>855-48-CM26</t>
+          <t>5147-90-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -26781,17 +26781,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26820,13 +26820,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>243.12</v>
+        <v>3126.31</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>902977-8-CM26</t>
+          <t>5147-91-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -26885,13 +26885,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>414.73</v>
+        <v>561.83</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>5147-91-CM26</t>
+          <t>902977-7-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -26950,13 +26950,13 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>561.83</v>
+        <v>500.54</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>902977-7-CM26</t>
+          <t>902977-8-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27015,13 +27015,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>500.54</v>
+        <v>414.73</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>5147-90-CM26</t>
+          <t>855-48-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -27041,17 +27041,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -27080,7 +27080,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>3126.31</v>
+        <v>243.12</v>
       </c>
     </row>
     <row r="426">
@@ -27541,7 +27541,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1000813-101-CM26</t>
+          <t>3225-6-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -27561,17 +27561,17 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>61.102.064-3</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -27581,17 +27581,17 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -27600,13 +27600,13 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>491.14</v>
+        <v>1039.97</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1536-87-CM26</t>
+          <t>1000813-101-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -27631,12 +27631,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -27646,17 +27646,17 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -27665,13 +27665,13 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>1241.09</v>
+        <v>491.14</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1536-88-CM26</t>
+          <t>1536-87-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -27730,13 +27730,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>4033.53</v>
+        <v>1241.09</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>3225-6-CM26</t>
+          <t>1536-88-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -27756,17 +27756,17 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>61.102.064-3</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27795,7 +27795,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1039.97</v>
+        <v>4033.53</v>
       </c>
     </row>
     <row r="437">
@@ -28126,7 +28126,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1116007-54-CM26</t>
+          <t>3617-58-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28146,17 +28146,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28185,13 +28185,13 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2798.74</v>
+        <v>6861.88</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>3617-58-CM26</t>
+          <t>855-57-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -28216,12 +28216,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -28250,7 +28250,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>6861.88</v>
+        <v>248.78</v>
       </c>
     </row>
     <row r="444">
@@ -28321,7 +28321,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>855-57-CM26</t>
+          <t>1116007-54-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -28341,17 +28341,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -28380,7 +28380,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>248.78</v>
+        <v>2798.74</v>
       </c>
     </row>
     <row r="446">
@@ -28841,7 +28841,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1233613-898-CM26</t>
+          <t>1233613-903-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -28900,13 +28900,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>3044.57</v>
+        <v>2558.46</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1233613-903-CM26</t>
+          <t>1069-42-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -28926,17 +28926,17 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -28965,13 +28965,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2558.46</v>
+        <v>1511.61</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1069-42-CM26</t>
+          <t>4589-182-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28996,12 +28996,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29030,7 +29030,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>1511.61</v>
+        <v>899.41</v>
       </c>
     </row>
     <row r="456">
@@ -29101,7 +29101,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>4589-182-CM26</t>
+          <t>1233613-898-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -29121,17 +29121,17 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>899.41</v>
+        <v>3044.57</v>
       </c>
     </row>
     <row r="458">
@@ -30011,7 +30011,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>1233613-943-CM26</t>
+          <t>1233613-942-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -30031,7 +30031,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -30051,12 +30051,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
@@ -30070,13 +30070,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1515.41</v>
+        <v>1923.29</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1233613-953-CM26</t>
+          <t>1233613-943-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -30135,13 +30135,13 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>3098.01</v>
+        <v>1515.41</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1233613-969-CM26</t>
+          <t>1233613-953-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -30200,13 +30200,13 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>3686.64</v>
+        <v>3098.01</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>958479-102-CM26</t>
+          <t>1233613-969-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -30226,17 +30226,17 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.980.720-0</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -30265,13 +30265,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>3098.01</v>
+        <v>3686.64</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>1079445-268-CM26</t>
+          <t>958479-102-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -30291,17 +30291,17 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.980.720-0</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -30330,13 +30330,13 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>1445.74</v>
+        <v>3098.01</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1233613-942-CM26</t>
+          <t>1079445-268-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -30361,12 +30361,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -30376,12 +30376,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
@@ -30395,7 +30395,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1923.29</v>
+        <v>1445.74</v>
       </c>
     </row>
     <row r="477">
@@ -30986,7 +30986,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1116007-65-CM26</t>
+          <t>796297-40-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31011,12 +31011,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>3011.06</v>
+        <v>1003.69</v>
       </c>
     </row>
     <row r="487">
@@ -31181,7 +31181,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>796297-40-CM26</t>
+          <t>1116007-65-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -31206,12 +31206,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -31240,7 +31240,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1003.69</v>
+        <v>3011.06</v>
       </c>
     </row>
     <row r="490">
@@ -31441,7 +31441,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>3617-75-CM26</t>
+          <t>3704-127-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -31466,12 +31466,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1111.79</v>
+        <v>881.91</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>3704-127-CM26</t>
+          <t>3617-75-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -31531,12 +31531,12 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -31565,13 +31565,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>881.91</v>
+        <v>1111.79</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>1079445-303-CM26</t>
+          <t>3268-301-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -31596,12 +31596,12 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -31630,13 +31630,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>1665.83</v>
+        <v>800.9299999999999</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1038-107-CM26</t>
+          <t>3412-81-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -31661,12 +31661,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -31695,13 +31695,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>6607.78</v>
+        <v>1668.6</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1079445-306-CM26</t>
+          <t>855-72-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -31726,12 +31726,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -31760,13 +31760,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>2114.49</v>
+        <v>832.91</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>1079445-305-CM26</t>
+          <t>855-73-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -31791,12 +31791,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -31825,7 +31825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1718.02</v>
+        <v>264.31</v>
       </c>
     </row>
     <row r="499">
@@ -31896,7 +31896,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>855-73-CM26</t>
+          <t>1079445-303-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -31921,12 +31921,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -31955,13 +31955,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>264.31</v>
+        <v>1665.83</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>855-72-CM26</t>
+          <t>1079445-305-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -31986,12 +31986,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -32020,13 +32020,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>832.91</v>
+        <v>1718.02</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>3412-81-CM26</t>
+          <t>1079445-306-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32051,12 +32051,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -32085,13 +32085,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>1668.6</v>
+        <v>2114.49</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>3268-301-CM26</t>
+          <t>1038-107-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -32116,12 +32116,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -32150,7 +32150,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>800.9299999999999</v>
+        <v>6607.78</v>
       </c>
     </row>
     <row r="504">
@@ -32351,7 +32351,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>5147-157-CM26</t>
+          <t>1038-110-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -32371,17 +32371,17 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -32410,13 +32410,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2066.32</v>
+        <v>6610.44</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>5147-158-CM26</t>
+          <t>5147-157-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -32475,13 +32475,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>4022.44</v>
+        <v>2066.32</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>902977-16-CM26</t>
+          <t>5147-158-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -32540,13 +32540,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>330.61</v>
+        <v>4022.44</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>902977-17-CM26</t>
+          <t>902977-16-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -32605,13 +32605,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>688.77</v>
+        <v>330.61</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1069-58-CM26</t>
+          <t>902977-17-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -32636,12 +32636,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1653.06</v>
+        <v>688.77</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1038-110-CM26</t>
+          <t>1069-58-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -32696,17 +32696,17 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -32735,7 +32735,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>6610.44</v>
+        <v>1653.06</v>
       </c>
     </row>
     <row r="513">
@@ -32806,7 +32806,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>855-78-CM26</t>
+          <t>3409-112-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -32831,12 +32831,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.101.455-4</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -32865,13 +32865,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>719.98</v>
+        <v>1107.66</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>3409-112-CM26</t>
+          <t>855-78-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -32896,12 +32896,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>61.101.455-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -32930,7 +32930,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1107.66</v>
+        <v>719.98</v>
       </c>
     </row>
     <row r="516">
@@ -33066,7 +33066,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>4589-271-CM26</t>
+          <t>855-85-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -33086,17 +33086,17 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -33125,13 +33125,13 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2171.78</v>
+        <v>410.88</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>3595-240-CM26</t>
+          <t>4589-271-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -33151,17 +33151,17 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -33171,17 +33171,17 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -33190,13 +33190,13 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1543.11</v>
+        <v>2171.78</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>855-85-CM26</t>
+          <t>3595-240-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -33221,12 +33221,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -33236,17 +33236,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -33255,7 +33255,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>410.88</v>
+        <v>1543.11</v>
       </c>
     </row>
     <row r="521">
@@ -33391,7 +33391,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1233613-1243-CM26</t>
+          <t>855-87-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -33416,12 +33416,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -33450,13 +33450,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>1469.9</v>
+        <v>489.97</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>3704-149-CM26</t>
+          <t>1233613-1243-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -33481,12 +33481,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -33515,13 +33515,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>783.95</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>855-87-CM26</t>
+          <t>3704-149-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -33546,12 +33546,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -33580,7 +33580,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>489.97</v>
+        <v>783.95</v>
       </c>
     </row>
     <row r="526">
@@ -34366,7 +34366,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>855-96-CM26</t>
+          <t>3704-173-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -34391,12 +34391,12 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -34425,13 +34425,13 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>493.5</v>
+        <v>1579.19</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>3704-173-CM26</t>
+          <t>855-97-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -34456,12 +34456,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -34490,13 +34490,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1579.19</v>
+        <v>740.25</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>855-97-CM26</t>
+          <t>855-96-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -34555,13 +34555,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>740.25</v>
+        <v>493.5</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1079445-380-CM26</t>
+          <t>1116007-88-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -34581,17 +34581,17 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -34620,13 +34620,13 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>580.98</v>
+        <v>2904.88</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>1116007-88-CM26</t>
+          <t>1079445-380-CM26</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -34646,17 +34646,17 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -34685,7 +34685,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2904.88</v>
+        <v>580.98</v>
       </c>
     </row>
     <row r="543">
@@ -35406,7 +35406,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>3704-188-CM26</t>
+          <t>3704-187-CM26</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -35471,7 +35471,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>3704-187-CM26</t>
+          <t>3704-188-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -35536,7 +35536,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1069-75-CM26</t>
+          <t>1233613-1330-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -35556,17 +35556,17 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -35595,13 +35595,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>1386.51</v>
+        <v>490.38</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1233613-1330-CM26</t>
+          <t>1233613-1331-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -35660,13 +35660,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>490.38</v>
+        <v>2334.19</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1233613-1323-CM26</t>
+          <t>1069-75-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -35686,17 +35686,17 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -35725,13 +35725,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>2917.74</v>
+        <v>1386.51</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>1233613-1331-CM26</t>
+          <t>1233613-1323-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -35790,13 +35790,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>2334.19</v>
+        <v>2917.74</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>902977-19-CM26</t>
+          <t>902977-18-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -35855,13 +35855,13 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>482.91</v>
+        <v>643.89</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>5147-196-CM26</t>
+          <t>902977-19-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -35920,13 +35920,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>2975.68</v>
+        <v>482.91</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>5147-197-CM26</t>
+          <t>5147-196-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -35985,13 +35985,13 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>827.85</v>
+        <v>2975.68</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>3595-286-CM26</t>
+          <t>5147-197-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36011,17 +36011,17 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -36031,12 +36031,12 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -36050,13 +36050,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>2109.05</v>
+        <v>827.85</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>855-104-CM26</t>
+          <t>3595-286-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -36081,12 +36081,12 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -36096,12 +36096,12 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
@@ -36115,13 +36115,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>218.92</v>
+        <v>2109.05</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>902977-18-CM26</t>
+          <t>855-104-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -36141,17 +36141,17 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -36180,7 +36180,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>643.89</v>
+        <v>218.92</v>
       </c>
     </row>
     <row r="566">
@@ -36251,7 +36251,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>3595-288-CM26</t>
+          <t>3268-438-CM26</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -36276,12 +36276,12 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -36291,17 +36291,17 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -36310,13 +36310,13 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>1548.58</v>
+        <v>643.12</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>855-105-CM26</t>
+          <t>3595-288-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -36341,12 +36341,12 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -36356,17 +36356,17 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
@@ -36375,13 +36375,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>367.49</v>
+        <v>1548.58</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>3268-438-CM26</t>
+          <t>855-105-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -36406,12 +36406,12 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -36440,13 +36440,13 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>643.12</v>
+        <v>367.49</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>1038-168-CM26</t>
+          <t>1116007-95-CM26</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -36466,17 +36466,17 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -36505,13 +36505,13 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>5417.7</v>
+        <v>2708.85</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>1116007-95-CM26</t>
+          <t>1038-168-CM26</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -36531,17 +36531,17 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -36570,13 +36570,13 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>2708.85</v>
+        <v>5417.7</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>1079445-431-CM26</t>
+          <t>855-110-CM26</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -36601,12 +36601,12 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -36635,13 +36635,13 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>1373.41</v>
+        <v>461.65</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>855-110-CM26</t>
+          <t>1079445-431-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -36700,7 +36700,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>461.65</v>
+        <v>1373.41</v>
       </c>
     </row>
     <row r="574">
@@ -36966,7 +36966,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>1470-30-CM26</t>
+          <t>3704-203-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -36986,17 +36986,17 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -37025,13 +37025,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>230.94</v>
+        <v>1477.99</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>3704-203-CM26</t>
+          <t>1470-30-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -37051,17 +37051,17 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -37090,7 +37090,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1477.99</v>
+        <v>230.94</v>
       </c>
     </row>
     <row r="580">
@@ -37291,7 +37291,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>796297-65-CM26</t>
+          <t>855-113-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -37316,12 +37316,12 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -37350,13 +37350,13 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>544.62</v>
+        <v>144.16</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>1079445-463-CM26</t>
+          <t>3704-211-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -37376,17 +37376,17 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -37415,13 +37415,13 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>1742.78</v>
+        <v>1464.52</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>3704-211-CM26</t>
+          <t>1079445-463-CM26</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -37441,17 +37441,17 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -37480,13 +37480,13 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>1464.52</v>
+        <v>1742.78</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>855-113-CM26</t>
+          <t>796297-65-CM26</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -37511,12 +37511,12 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -37545,7 +37545,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>144.16</v>
+        <v>544.62</v>
       </c>
     </row>
     <row r="587">
@@ -37876,7 +37876,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>855-119-CM26</t>
+          <t>796297-64-CM26</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -37901,12 +37901,12 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -37935,13 +37935,13 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>458.71</v>
+        <v>1557.46</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>855-118-CM26</t>
+          <t>855-119-CM26</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38000,13 +38000,13 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>409.4</v>
+        <v>458.71</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>796297-64-CM26</t>
+          <t>855-118-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -38031,12 +38031,12 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -38065,7 +38065,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>1557.46</v>
+        <v>409.4</v>
       </c>
     </row>
     <row r="595">
@@ -38266,7 +38266,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>958479-184-CM26</t>
+          <t>1470-31-CM26</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -38291,12 +38291,12 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>61.980.720-0</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -38325,13 +38325,13 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>2781.58</v>
+        <v>556.3200000000001</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1470-31-CM26</t>
+          <t>958479-184-CM26</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -38356,12 +38356,12 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>61.980.720-0</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -38390,7 +38390,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>556.3200000000001</v>
+        <v>2781.58</v>
       </c>
     </row>
     <row r="600">
@@ -39696,7 +39696,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>855-141-CM26</t>
+          <t>1038-195-CM26</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -39721,12 +39721,12 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>347.82</v>
+        <v>5351.13</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>1038-195-CM26</t>
+          <t>855-141-CM26</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -39786,12 +39786,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -39820,13 +39820,13 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>5351.13</v>
+        <v>347.82</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>3595-334-CM26</t>
+          <t>4589-366-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -39846,17 +39846,17 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -39866,17 +39866,17 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
@@ -39885,13 +39885,13 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>2004.13</v>
+        <v>12912.35</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>4589-366-CM26</t>
+          <t>3595-333-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -39911,17 +39911,17 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -39950,13 +39950,13 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>12912.35</v>
+        <v>1547.35</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>3704-237-CM26</t>
+          <t>3595-334-CM26</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -39976,17 +39976,17 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -39996,12 +39996,12 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -40015,13 +40015,13 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1434.8</v>
+        <v>2004.13</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>3595-333-CM26</t>
+          <t>3704-237-CM26</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -40041,17 +40041,17 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -40061,17 +40061,17 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
@@ -40080,7 +40080,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>1547.35</v>
+        <v>1434.8</v>
       </c>
     </row>
     <row r="626">
@@ -40736,7 +40736,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>1079445-563-CM26</t>
+          <t>3409-177-CM26</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -40756,17 +40756,17 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.101.455-4</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -40795,13 +40795,13 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>525.24</v>
+        <v>1575.71</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>1079445-564-CM26</t>
+          <t>1079445-563-CM26</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -40860,13 +40860,13 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1313.09</v>
+        <v>525.24</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>3409-177-CM26</t>
+          <t>1079445-564-CM26</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -40886,17 +40886,17 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>61.101.455-4</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -40925,7 +40925,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1575.71</v>
+        <v>1313.09</v>
       </c>
     </row>
     <row r="639">
@@ -41776,7 +41776,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>855-149-CM26</t>
+          <t>1116007-130-CM26</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -41796,17 +41796,17 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -41835,13 +41835,13 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>434.97</v>
+        <v>2588.07</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>1116007-129-CM26</t>
+          <t>855-149-CM26</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -41861,17 +41861,17 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -41900,13 +41900,13 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>1304.91</v>
+        <v>434.97</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>1116007-130-CM26</t>
+          <t>1116007-129-CM26</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -41965,7 +41965,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2588.07</v>
+        <v>1304.91</v>
       </c>
     </row>
     <row r="655">
@@ -42621,7 +42621,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>1536-188-CM26</t>
+          <t>3412-140-CM26</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -42641,17 +42641,17 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -42661,17 +42661,17 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L665" t="inlineStr">
@@ -42680,13 +42680,13 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2835.24</v>
+        <v>1047.5</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>3412-140-CM26</t>
+          <t>1536-188-CM26</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -42706,17 +42706,17 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -42726,17 +42726,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -42745,7 +42745,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>1047.5</v>
+        <v>2835.24</v>
       </c>
     </row>
     <row r="667">
@@ -43206,7 +43206,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>4589-435-CM26</t>
+          <t>1116007-152-CM26</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -43231,12 +43231,12 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -43246,17 +43246,17 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -43265,13 +43265,13 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>605.48</v>
+        <v>2553.91</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>1116007-152-CM26</t>
+          <t>4589-437-CM26</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -43296,12 +43296,12 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -43311,17 +43311,17 @@
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L675" t="inlineStr">
@@ -43330,13 +43330,13 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2553.91</v>
+        <v>4238.88</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>4589-437-CM26</t>
+          <t>4589-435-CM26</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>4238.88</v>
+        <v>605.48</v>
       </c>
     </row>
     <row r="677">
@@ -44116,7 +44116,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>1233613-1831-CM26</t>
+          <t>1233613-1832-CM26</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -44175,13 +44175,13 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>1303.95</v>
+        <v>434.65</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>1233613-1832-CM26</t>
+          <t>1233613-1831-CM26</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -44240,7 +44240,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>434.65</v>
+        <v>1303.95</v>
       </c>
     </row>
     <row r="690">
@@ -45286,7 +45286,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>1536-216-CM26</t>
+          <t>3268-776-CM26</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -45311,12 +45311,12 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -45326,17 +45326,17 @@
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
@@ -45345,13 +45345,13 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>4992.58</v>
+        <v>771.14</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>3268-776-CM26</t>
+          <t>1536-216-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -45376,12 +45376,12 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -45391,17 +45391,17 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
@@ -45410,13 +45410,13 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>771.14</v>
+        <v>4992.58</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>4589-466-CM26</t>
+          <t>4589-467-CM26</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -45475,13 +45475,13 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>5271.57</v>
+        <v>1432.49</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>4589-467-CM26</t>
+          <t>3595-405-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -45506,12 +45506,12 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -45540,13 +45540,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1432.49</v>
+        <v>1547.09</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>3595-405-CM26</t>
+          <t>4589-466-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -45571,12 +45571,12 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -45605,7 +45605,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1547.09</v>
+        <v>5271.57</v>
       </c>
     </row>
     <row r="711">
@@ -45741,7 +45741,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>1116007-170-CM26</t>
+          <t>855-216-CM26</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -45766,12 +45766,12 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -45800,13 +45800,13 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1465.34</v>
+        <v>174.38</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>855-216-CM26</t>
+          <t>1116007-170-CM26</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -45831,12 +45831,12 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -45865,13 +45865,13 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>174.38</v>
+        <v>1465.34</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>1079445-677-CM26</t>
+          <t>5147-308-CM26</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -45896,12 +45896,12 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -45930,13 +45930,13 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>1855.88</v>
+        <v>3699.08</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>5147-308-CM26</t>
+          <t>902977-27-CM26</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -45995,13 +45995,13 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>3699.08</v>
+        <v>536.1</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>902977-27-CM26</t>
+          <t>1079445-677-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -46026,12 +46026,12 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -46060,7 +46060,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>536.1</v>
+        <v>1855.88</v>
       </c>
     </row>
     <row r="718">
@@ -46456,65 +46456,130 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
+          <t>3595-421-CM26</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>69.251.400-9</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M724" s="2" t="n">
+        <v>1725.61</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
           <t>3617-126-CM26</t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>2239-1-LR25</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D724" t="inlineStr">
+      <c r="D725" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E724" t="inlineStr">
+      <c r="E725" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F724" t="inlineStr">
+      <c r="F725" t="inlineStr">
         <is>
           <t>61.313.000-4</t>
         </is>
       </c>
-      <c r="G724" t="inlineStr">
+      <c r="G725" t="inlineStr">
         <is>
           <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
-      <c r="H724" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="I724" t="inlineStr">
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
         </is>
       </c>
-      <c r="J724" t="inlineStr">
+      <c r="J725" t="inlineStr">
         <is>
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr">
+      <c r="K725" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L724" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M724" s="2" t="n">
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M725" s="2" t="n">
         <v>57328.64</v>
       </c>
     </row>
